--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD4FA96-BDEB-48C2-AEA8-0509BF37A4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F4954D-A741-4E5B-B17C-0C22C836E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -60,19 +60,28 @@
     <t>Currency</t>
   </si>
   <si>
+    <t>30-JUL-26</t>
+  </si>
+  <si>
+    <t>SM-490</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-640</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
     <t>24-SEP-26</t>
   </si>
   <si>
-    <t>SM-490</t>
-  </si>
-  <si>
     <t>flynas XY-793</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>SAR</t>
+    <t>MED</t>
   </si>
   <si>
     <t>flynas XY-576</t>
@@ -105,7 +114,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +131,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD4EDDA"/>
         <bgColor rgb="FFD4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -161,6 +176,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -527,22 +545,22 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="E2" s="2">
-        <v>898</v>
+        <v>447</v>
       </c>
       <c r="F2" s="2">
-        <v>-519</v>
+        <v>-33</v>
       </c>
       <c r="G2" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2">
         <v>30</v>
       </c>
       <c r="I2" s="2">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -553,34 +571,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2">
-        <v>379</v>
+        <v>570</v>
       </c>
       <c r="E3" s="2">
         <v>898</v>
       </c>
       <c r="F3" s="2">
-        <v>-519</v>
+        <v>-328</v>
       </c>
       <c r="G3" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2">
         <v>30</v>
       </c>
       <c r="I3" s="2">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -588,36 +606,71 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>409</v>
+        <v>570</v>
       </c>
       <c r="E4" s="2">
         <v>898</v>
       </c>
       <c r="F4" s="2">
-        <v>-489</v>
+        <v>-328</v>
       </c>
       <c r="G4" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2">
         <v>30</v>
       </c>
       <c r="I4" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2">
+        <v>579</v>
+      </c>
+      <c r="E5" s="2">
+        <v>898</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-319</v>
+      </c>
+      <c r="G5" s="2">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
